--- a/src/src/main/webapp/portal/zkb/trainV2/trainRecord/APM_ZKB_FE_Train_Record_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/trainV2/trainRecord/APM_ZKB_FE_Train_Record_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\223032910\Box\我的 Box Notes\13-ZKB Offer\ZKB运营支持相关\APM FE培训管理模块\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gehealthcare-my.sharepoint.com/personal/550004857_gehealthcare_com/Documents/Desktop/智康宝/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{984CDC92-38A1-4C98-9FC5-8939D4F0C11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{984CDC92-38A1-4C98-9FC5-8939D4F0C11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{946BA33C-C53F-449D-BF37-EE8B77EA5FA6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0831852C-F913-4250-8866-AE4825699531}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{0831852C-F913-4250-8866-AE4825699531}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Status</t>
   </si>
@@ -89,30 +89,12 @@
     <t>电话</t>
   </si>
   <si>
-    <t>邮箱</t>
-  </si>
-  <si>
     <t>身份证号</t>
   </si>
   <si>
-    <t>商备邮件</t>
-  </si>
-  <si>
     <t>Online</t>
   </si>
   <si>
-    <t>Lab+笔试</t>
-  </si>
-  <si>
-    <t>Final</t>
-  </si>
-  <si>
-    <t>Degree</t>
-  </si>
-  <si>
-    <t>是否通过</t>
-  </si>
-  <si>
     <t>Attended</t>
   </si>
   <si>
@@ -158,20 +140,26 @@
     <t>307141426@qq.com</t>
   </si>
   <si>
-    <t>40+48</t>
-  </si>
-  <si>
-    <t>良好</t>
-  </si>
-  <si>
-    <t>通过</t>
+    <t>个人邮箱</t>
+  </si>
+  <si>
+    <t>商务邮箱</t>
+  </si>
+  <si>
+    <t>课堂实验</t>
+  </si>
+  <si>
+    <t>考试</t>
+  </si>
+  <si>
+    <t>总分</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,38 +173,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Source Han Sans CN Normal"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Source Han Sans CN Normal"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Source Han Sans CN Medium"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Source Han Sans CN Normal"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
       <u/>
@@ -260,6 +216,20 @@
       <name val="Source Han Sans CN Normal"/>
       <family val="2"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -294,67 +264,61 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -373,6 +337,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -693,161 +661,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8008609F-C55E-4DE4-9E79-DDF00DA6743A}">
   <dimension ref="A1:X2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.83984375" customWidth="1"/>
+    <col min="4" max="4" width="17.68359375" customWidth="1"/>
+    <col min="5" max="5" width="24.41796875" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="14.734375" customWidth="1"/>
+    <col min="15" max="15" width="11.5234375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.3125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:24" s="15" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="R1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="U1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="D2" s="4">
+        <v>45839</v>
+      </c>
+      <c r="E2" s="4">
+        <v>45839</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="G2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="H2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="I2" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11" t="s">
+      <c r="K2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="12">
-        <v>45664</v>
-      </c>
-      <c r="E2" s="12">
-        <v>45667</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="L2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="M2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="N2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="O2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="P2" s="5">
+        <v>13115226924</v>
+      </c>
+      <c r="Q2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="R2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="S2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="O2" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="13">
-        <v>13115226924</v>
-      </c>
-      <c r="Q2" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="V2" s="9">
+      <c r="T2" s="1"/>
+      <c r="U2" s="1">
+        <v>40</v>
+      </c>
+      <c r="V2" s="1">
+        <v>48</v>
+      </c>
+      <c r="W2" s="1">
         <v>88</v>
       </c>
-      <c r="W2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" s="9" t="s">
-        <v>41</v>
-      </c>
+      <c r="X2" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="I1" xr:uid="{5DFE3D51-A9CD-4065-9199-2C73FB29F974}">
+    <dataValidation type="list" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="I1" xr:uid="{4A0959D5-5B47-47EC-AB4A-942DD260BC55}">
       <formula1>"Online, Offline"</formula1>
     </dataValidation>
   </dataValidations>
